--- a/doc/OOO_스케쥴_수정.xlsx
+++ b/doc/OOO_스케쥴_수정.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\melephant\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6086002-4780-437E-9B64-87DBA550698D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A3AA57-5898-435B-BC28-ADBF0285D03A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{8ABF4B1D-5BC9-42F2-ACF5-909D4BBB9E92}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>학생</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -108,6 +108,10 @@
   </si>
   <si>
     <t>==&gt; 정렬순서</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>==&gt; 0: 일, 1: 월, 2: 화, 3: 수, 4:목, 5: 금, 6: 토</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -115,9 +119,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -196,7 +197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -218,10 +219,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -551,7 +555,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>18</v>
       </c>
     </row>
@@ -637,10 +641,12 @@
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>44732</v>
-      </c>
-      <c r="B12" s="5"/>
+      <c r="A12" s="8">
+        <v>0</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
